--- a/N5/test/categorized testing/CategorizedtestScenarios.xlsx
+++ b/N5/test/categorized testing/CategorizedtestScenarios.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Re-run 2026-05-24: Pass=176 Fail=2 Partial=0 N/A=0 (of 178 patterns). Failing: n5-026, n5-144. See BUG-202.</t>
+          <t>Re-run 2026-05-24 post-fix: Pass=178 Fail=0 Partial=0 N/A=0 (of 178 patterns). BUG-211 (GRAMMAR-CT-001) resolved via Option A rewrite on n5-026 + n5-144 cm[0]; both now carry real JA-JA wrong/right pairs.</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Fail (programmatic) (2026-05-24) — cm[0].right has no Japanese: 'Drop the particle in writing.'</t>
+          <t>Pass (programmatic — BUG-211 Option A rewrite) (2026-05-24)</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="Q18" s="11" t="inlineStr">
         <is>
-          <t>Fail (2026-05-24)</t>
+          <t>Pass (2026-05-24)</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>See bug tracker BUG-202 (GRAMMAR-CT-001): cm[0].right has no Japanese: 'Drop the particle in writing.'</t>
+          <t>BUG-211 resolved via Option A rewrite v1.16.12</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>Fail (programmatic) (2026-05-24) — cm[0].right has no Japanese: 'Same subject for both verbs.'</t>
+          <t>Pass (programmatic — BUG-211 Option A rewrite) (2026-05-24)</t>
         </is>
       </c>
       <c r="J141" s="10" t="inlineStr">
@@ -13661,12 +13661,12 @@
       </c>
       <c r="Q141" s="11" t="inlineStr">
         <is>
-          <t>Fail (2026-05-24)</t>
+          <t>Pass (2026-05-24)</t>
         </is>
       </c>
       <c r="R141" s="6" t="inlineStr">
         <is>
-          <t>See bug tracker BUG-202 (GRAMMAR-CT-001): cm[0].right has no Japanese: 'Same subject for both verbs.'</t>
+          <t>BUG-211 resolved via Option A rewrite v1.16.12</t>
         </is>
       </c>
     </row>

--- a/N5/test/categorized testing/CategorizedtestScenarios.xlsx
+++ b/N5/test/categorized testing/CategorizedtestScenarios.xlsx
@@ -1367,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R179"/>
+  <dimension ref="A1:U179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="3.81640625" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
@@ -1473,6 +1473,21 @@
           <t>Bug Details / Notes</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Reviewed Date</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Native Review Status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="84" customHeight="1" s="15">
       <c r="A2" s="6" t="n">
@@ -1559,6 +1574,21 @@
         </is>
       </c>
       <c r="R2" s="6" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="84" customHeight="1" s="15">
       <c r="A3" s="6" t="n">
@@ -1645,6 +1675,21 @@
         </is>
       </c>
       <c r="R3" s="6" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="84" customHeight="1" s="15">
       <c r="A4" s="6" t="n">
@@ -1731,6 +1776,21 @@
         </is>
       </c>
       <c r="R4" s="6" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="84" customHeight="1" s="15">
       <c r="A5" s="6" t="n">
@@ -1817,6 +1877,21 @@
         </is>
       </c>
       <c r="R5" s="6" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="84" customHeight="1" s="15">
       <c r="A6" s="6" t="n">
@@ -1903,6 +1978,21 @@
         </is>
       </c>
       <c r="R6" s="6" t="n"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="84" customHeight="1" s="15">
       <c r="A7" s="6" t="n">
@@ -1989,6 +2079,21 @@
         </is>
       </c>
       <c r="R7" s="6" t="n"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="84" customHeight="1" s="15">
       <c r="A8" s="6" t="n">
@@ -2075,6 +2180,21 @@
         </is>
       </c>
       <c r="R8" s="6" t="n"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="84" customHeight="1" s="15">
       <c r="A9" s="6" t="n">
@@ -2161,6 +2281,21 @@
         </is>
       </c>
       <c r="R9" s="6" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="84" customHeight="1" s="15">
       <c r="A10" s="6" t="n">
@@ -2247,6 +2382,21 @@
         </is>
       </c>
       <c r="R10" s="6" t="n"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="84" customHeight="1" s="15">
       <c r="A11" s="6" t="n">
@@ -2333,6 +2483,21 @@
         </is>
       </c>
       <c r="R11" s="6" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="84" customHeight="1" s="15">
       <c r="A12" s="6" t="n">
@@ -2423,6 +2588,21 @@
           <t>[TS-03] Class C - common_mistakes[2] labelled 'りんごと バナナを たべます。' as wrong vs 'りんごや バナナを たべます。' - both valid Japanese with different meanings (exhaustive vs non-exhaustive listing); conflated meaning-choice with grammatical error. || Fix: Data fix: row replaced with a genuine learner error (missing connecting particle entirely) via tools/fix_remaining_grammar_bugs_2026_05_24.py.</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="84" customHeight="1" s="15">
       <c r="A13" s="6" t="n">
@@ -2509,6 +2689,21 @@
         </is>
       </c>
       <c r="R13" s="6" t="n"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="84" customHeight="1" s="15">
       <c r="A14" s="6" t="n">
@@ -2599,6 +2794,21 @@
           <t>[TS-03] Class D - common_mistakes[1] wrong field contained '9時から 5時まで しごとです。 -&gt; 9時で 5時まで' with an in-cell arrow joining the right sentence to a wrong fragment. || Fix: Data fix: row repaired via tools/fix_class_d_arrow_cells_2026_05_24.py - extracted the true learner mistake into a clean wrong sentence; diagnostic transformation kept in why field.</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="84" customHeight="1" s="15">
       <c r="A15" s="6" t="n">
@@ -2689,6 +2899,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="84" customHeight="1" s="15">
       <c r="A16" s="6" t="n">
@@ -2779,6 +3004,21 @@
           <t>[TS-03] Class C - common_mistakes[1] labelled 'コーヒーと おちゃが いいです。' as wrong vs 'コーヒーか おちゃが いいです。' - both valid Japanese; と version means 'I want coffee AND tea', か version means 'either coffee OR tea'. || Fix: Data fix: row replaced with a genuine learner error (missing connecting particle entirely) via tools/fix_remaining_grammar_bugs_2026_05_24.py.</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="84" customHeight="1" s="15">
       <c r="A17" s="6" t="n">
@@ -2865,6 +3105,21 @@
         </is>
       </c>
       <c r="R17" s="6" t="n"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="84" customHeight="1" s="15">
       <c r="A18" s="6" t="n">
@@ -2955,6 +3210,21 @@
           <t>BUG-211 resolved via Option A rewrite v1.16.12</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="84" customHeight="1" s="15">
       <c r="A19" s="6" t="n">
@@ -3041,6 +3311,21 @@
         </is>
       </c>
       <c r="R19" s="6" t="n"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="84" customHeight="1" s="15">
       <c r="A20" s="6" t="n">
@@ -3127,6 +3412,21 @@
         </is>
       </c>
       <c r="R20" s="6" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="84" customHeight="1" s="15">
       <c r="A21" s="6" t="n">
@@ -3213,6 +3513,21 @@
         </is>
       </c>
       <c r="R21" s="6" t="n"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="84" customHeight="1" s="15">
       <c r="A22" s="6" t="n">
@@ -3303,6 +3618,21 @@
           <t>[TS-03] Class D - common_mistakes[0] wrong contained '日本語を勉強するのが好きだ。 -&gt; 日本語の勉強。' with in-cell arrow. || Fix: Data fix: row repaired via tools/fix_class_d_arrow_cells_2026_05_24.py - extracted the true learner mistake into a clean wrong sentence; diagnostic transformation kept in why field.</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="84" customHeight="1" s="15">
       <c r="A23" s="6" t="n">
@@ -3389,6 +3719,21 @@
         </is>
       </c>
       <c r="R23" s="6" t="n"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="84" customHeight="1" s="15">
       <c r="A24" s="6" t="n">
@@ -3475,6 +3820,21 @@
         </is>
       </c>
       <c r="R24" s="6" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="84" customHeight="1" s="15">
       <c r="A25" s="6" t="n">
@@ -3561,6 +3921,21 @@
         </is>
       </c>
       <c r="R25" s="6" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="84" customHeight="1" s="15">
       <c r="A26" s="6" t="n">
@@ -3647,6 +4022,21 @@
         </is>
       </c>
       <c r="R26" s="6" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="84" customHeight="1" s="15">
       <c r="A27" s="6" t="n">
@@ -3733,6 +4123,21 @@
         </is>
       </c>
       <c r="R27" s="6" t="n"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="84" customHeight="1" s="15">
       <c r="A28" s="6" t="n">
@@ -3819,6 +4224,21 @@
         </is>
       </c>
       <c r="R28" s="6" t="n"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="84" customHeight="1" s="15">
       <c r="A29" s="6" t="n">
@@ -3905,6 +4325,21 @@
         </is>
       </c>
       <c r="R29" s="6" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="84" customHeight="1" s="15">
       <c r="A30" s="6" t="n">
@@ -3991,6 +4426,21 @@
         </is>
       </c>
       <c r="R30" s="6" t="n"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="84" customHeight="1" s="15">
       <c r="A31" s="6" t="n">
@@ -4077,6 +4527,21 @@
         </is>
       </c>
       <c r="R31" s="6" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="84" customHeight="1" s="15">
       <c r="A32" s="6" t="n">
@@ -4163,6 +4628,21 @@
         </is>
       </c>
       <c r="R32" s="6" t="n"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="84" customHeight="1" s="15">
       <c r="A33" s="6" t="n">
@@ -4249,6 +4729,21 @@
         </is>
       </c>
       <c r="R33" s="6" t="n"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="84" customHeight="1" s="15">
       <c r="A34" s="6" t="n">
@@ -4339,6 +4834,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="84" customHeight="1" s="15">
       <c r="A35" s="6" t="n">
@@ -4425,6 +4935,21 @@
         </is>
       </c>
       <c r="R35" s="6" t="n"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="84" customHeight="1" s="15">
       <c r="A36" s="6" t="n">
@@ -4515,6 +5040,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="84" customHeight="1" s="15">
       <c r="A37" s="6" t="n">
@@ -4605,6 +5145,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="84" customHeight="1" s="15">
       <c r="A38" s="6" t="n">
@@ -4695,6 +5250,21 @@
           <t>[TS-03] Class D + FP-16 - this pattern had two findings: (a) common_mistakes carried an in-cell arrow breaking the wrong/right contract, AND (b) a different cm row was a register_variant entry misidentified as empty wrong/right. || Fix: Two-part fix: (a) data repaired via tools/fix_class_d_arrow_cells_2026_05_24.py (arrow extracted, clean wrong sentence written); (b) test logic corrected to skip register_variant entries.</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="84" customHeight="1" s="15">
       <c r="A39" s="6" t="n">
@@ -4781,6 +5351,21 @@
         </is>
       </c>
       <c r="R39" s="6" t="n"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="84" customHeight="1" s="15">
       <c r="A40" s="6" t="n">
@@ -4871,6 +5456,21 @@
           <t>[TS-03] Class D + FP-16 - this pattern had two findings: (a) common_mistakes carried an in-cell arrow breaking the wrong/right contract, AND (b) a different cm row was a register_variant entry misidentified as empty wrong/right. || Fix: Two-part fix: (a) data repaired via tools/fix_class_d_arrow_cells_2026_05_24.py (arrow extracted, clean wrong sentence written); (b) test logic corrected to skip register_variant entries.</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="84" customHeight="1" s="15">
       <c r="A41" s="6" t="n">
@@ -4957,6 +5557,21 @@
         </is>
       </c>
       <c r="R41" s="6" t="n"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="84" customHeight="1" s="15">
       <c r="A42" s="6" t="n">
@@ -5047,6 +5662,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="84" customHeight="1" s="15">
       <c r="A43" s="6" t="n">
@@ -5137,6 +5767,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="84" customHeight="1" s="15">
       <c r="A44" s="6" t="n">
@@ -5227,6 +5872,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="84" customHeight="1" s="15">
       <c r="A45" s="6" t="n">
@@ -5317,6 +5977,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="84" customHeight="1" s="15">
       <c r="A46" s="6" t="n">
@@ -5407,6 +6082,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="84" customHeight="1" s="15">
       <c r="A47" s="6" t="n">
@@ -5497,6 +6187,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="84" customHeight="1" s="15">
       <c r="A48" s="6" t="n">
@@ -5583,6 +6288,21 @@
         </is>
       </c>
       <c r="R48" s="6" t="n"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="84" customHeight="1" s="15">
       <c r="A49" s="6" t="n">
@@ -5669,6 +6389,21 @@
         </is>
       </c>
       <c r="R49" s="6" t="n"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="84" customHeight="1" s="15">
       <c r="A50" s="6" t="n">
@@ -5755,6 +6490,21 @@
         </is>
       </c>
       <c r="R50" s="6" t="n"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="84" customHeight="1" s="15">
       <c r="A51" s="6" t="n">
@@ -5841,6 +6591,21 @@
         </is>
       </c>
       <c r="R51" s="6" t="n"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="84" customHeight="1" s="15">
       <c r="A52" s="6" t="n">
@@ -5927,6 +6692,21 @@
         </is>
       </c>
       <c r="R52" s="6" t="n"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="84" customHeight="1" s="15">
       <c r="A53" s="6" t="n">
@@ -6013,6 +6793,21 @@
         </is>
       </c>
       <c r="R53" s="6" t="n"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="84" customHeight="1" s="15">
       <c r="A54" s="6" t="n">
@@ -6099,6 +6894,21 @@
         </is>
       </c>
       <c r="R54" s="6" t="n"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="84" customHeight="1" s="15">
       <c r="A55" s="6" t="n">
@@ -6185,6 +6995,21 @@
         </is>
       </c>
       <c r="R55" s="6" t="n"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="84" customHeight="1" s="15">
       <c r="A56" s="6" t="n">
@@ -6275,6 +7100,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="84" customHeight="1" s="15">
       <c r="A57" s="6" t="n">
@@ -6361,6 +7201,21 @@
         </is>
       </c>
       <c r="R57" s="6" t="n"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="84" customHeight="1" s="15">
       <c r="A58" s="6" t="n">
@@ -6447,6 +7302,21 @@
         </is>
       </c>
       <c r="R58" s="6" t="n"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="84" customHeight="1" s="15">
       <c r="A59" s="6" t="n">
@@ -6533,6 +7403,21 @@
         </is>
       </c>
       <c r="R59" s="6" t="n"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="84" customHeight="1" s="15">
       <c r="A60" s="6" t="n">
@@ -6619,6 +7504,21 @@
         </is>
       </c>
       <c r="R60" s="6" t="n"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="84" customHeight="1" s="15">
       <c r="A61" s="6" t="n">
@@ -6705,6 +7605,21 @@
         </is>
       </c>
       <c r="R61" s="6" t="n"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="84" customHeight="1" s="15">
       <c r="A62" s="6" t="n">
@@ -6791,6 +7706,21 @@
         </is>
       </c>
       <c r="R62" s="6" t="n"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="84" customHeight="1" s="15">
       <c r="A63" s="6" t="n">
@@ -6881,6 +7811,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="84" customHeight="1" s="15">
       <c r="A64" s="6" t="n">
@@ -6967,6 +7912,21 @@
         </is>
       </c>
       <c r="R64" s="6" t="n"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="84" customHeight="1" s="15">
       <c r="A65" s="6" t="n">
@@ -7053,6 +8013,21 @@
         </is>
       </c>
       <c r="R65" s="6" t="n"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="84" customHeight="1" s="15">
       <c r="A66" s="6" t="n">
@@ -7139,6 +8114,21 @@
         </is>
       </c>
       <c r="R66" s="6" t="n"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="84" customHeight="1" s="15">
       <c r="A67" s="6" t="n">
@@ -7225,6 +8215,21 @@
         </is>
       </c>
       <c r="R67" s="6" t="n"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="84" customHeight="1" s="15">
       <c r="A68" s="6" t="n">
@@ -7315,6 +8320,21 @@
           <t>[TS-03] Class D - common_mistakes[0] wrong AND right BOTH contained arrows: 'いく -&gt; いいた' / 'いく -&gt; いった' (conjugation arrows used as wrong/right cells). || Fix: Data fix: arrows lifted into a full-sentence wrong/right pair via tools/fix_class_d_arrow_cells_2026_05_24.py.</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="84" customHeight="1" s="15">
       <c r="A69" s="6" t="n">
@@ -7401,6 +8421,21 @@
         </is>
       </c>
       <c r="R69" s="6" t="n"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="84" customHeight="1" s="15">
       <c r="A70" s="6" t="n">
@@ -7491,6 +8526,21 @@
           <t>[TS-03] Class D + FP-16 - this pattern had two findings: (a) common_mistakes carried an in-cell arrow breaking the wrong/right contract, AND (b) a different cm row was a register_variant entry misidentified as empty wrong/right. || Fix: Two-part fix: (a) data repaired via tools/fix_class_d_arrow_cells_2026_05_24.py (arrow extracted, clean wrong sentence written); (b) test logic corrected to skip register_variant entries.</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="84" customHeight="1" s="15">
       <c r="A71" s="6" t="n">
@@ -7577,6 +8627,21 @@
         </is>
       </c>
       <c r="R71" s="6" t="n"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="84" customHeight="1" s="15">
       <c r="A72" s="6" t="n">
@@ -7667,6 +8732,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="84" customHeight="1" s="15">
       <c r="A73" s="6" t="n">
@@ -7753,6 +8833,21 @@
         </is>
       </c>
       <c r="R73" s="6" t="n"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="84" customHeight="1" s="15">
       <c r="A74" s="6" t="n">
@@ -7839,6 +8934,21 @@
         </is>
       </c>
       <c r="R74" s="6" t="n"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="84" customHeight="1" s="15">
       <c r="A75" s="6" t="n">
@@ -7929,6 +9039,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="84" customHeight="1" s="15">
       <c r="A76" s="6" t="n">
@@ -8019,6 +9144,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="84" customHeight="1" s="15">
       <c r="A77" s="6" t="n">
@@ -8105,6 +9245,21 @@
         </is>
       </c>
       <c r="R77" s="6" t="n"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="84" customHeight="1" s="15">
       <c r="A78" s="6" t="n">
@@ -8195,6 +9350,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="84" customHeight="1" s="15">
       <c r="A79" s="6" t="n">
@@ -8281,6 +9451,21 @@
         </is>
       </c>
       <c r="R79" s="6" t="n"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="84" customHeight="1" s="15">
       <c r="A80" s="6" t="n">
@@ -8367,6 +9552,21 @@
         </is>
       </c>
       <c r="R80" s="6" t="n"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="84" customHeight="1" s="15">
       <c r="A81" s="6" t="n">
@@ -8453,6 +9653,21 @@
         </is>
       </c>
       <c r="R81" s="6" t="n"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="84" customHeight="1" s="15">
       <c r="A82" s="6" t="n">
@@ -8539,6 +9754,21 @@
         </is>
       </c>
       <c r="R82" s="6" t="n"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="84" customHeight="1" s="15">
       <c r="A83" s="6" t="n">
@@ -8625,6 +9855,21 @@
         </is>
       </c>
       <c r="R83" s="6" t="n"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="84" customHeight="1" s="15">
       <c r="A84" s="6" t="n">
@@ -8711,6 +9956,21 @@
         </is>
       </c>
       <c r="R84" s="6" t="n"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="84" customHeight="1" s="15">
       <c r="A85" s="6" t="n">
@@ -8797,6 +10057,21 @@
         </is>
       </c>
       <c r="R85" s="6" t="n"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="84" customHeight="1" s="15">
       <c r="A86" s="6" t="n">
@@ -8883,6 +10158,21 @@
         </is>
       </c>
       <c r="R86" s="6" t="n"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="84" customHeight="1" s="15">
       <c r="A87" s="6" t="n">
@@ -8969,6 +10259,21 @@
         </is>
       </c>
       <c r="R87" s="6" t="n"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="84" customHeight="1" s="15">
       <c r="A88" s="6" t="n">
@@ -9055,6 +10360,21 @@
         </is>
       </c>
       <c r="R88" s="6" t="n"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="84" customHeight="1" s="15">
       <c r="A89" s="6" t="n">
@@ -9141,6 +10461,21 @@
         </is>
       </c>
       <c r="R89" s="6" t="n"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="84" customHeight="1" s="15">
       <c r="A90" s="6" t="n">
@@ -9227,6 +10562,21 @@
         </is>
       </c>
       <c r="R90" s="6" t="n"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="84" customHeight="1" s="15">
       <c r="A91" s="6" t="n">
@@ -9313,6 +10663,21 @@
         </is>
       </c>
       <c r="R91" s="6" t="n"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="84" customHeight="1" s="15">
       <c r="A92" s="6" t="n">
@@ -9399,6 +10764,21 @@
         </is>
       </c>
       <c r="R92" s="6" t="n"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="84" customHeight="1" s="15">
       <c r="A93" s="6" t="n">
@@ -9485,6 +10865,21 @@
         </is>
       </c>
       <c r="R93" s="6" t="n"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="84" customHeight="1" s="15">
       <c r="A94" s="6" t="n">
@@ -9571,6 +10966,21 @@
         </is>
       </c>
       <c r="R94" s="6" t="n"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="84" customHeight="1" s="15">
       <c r="A95" s="6" t="n">
@@ -9657,6 +11067,21 @@
         </is>
       </c>
       <c r="R95" s="6" t="n"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="84" customHeight="1" s="15">
       <c r="A96" s="6" t="n">
@@ -9743,6 +11168,21 @@
         </is>
       </c>
       <c r="R96" s="6" t="n"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="84" customHeight="1" s="15">
       <c r="A97" s="6" t="n">
@@ -9829,6 +11269,21 @@
         </is>
       </c>
       <c r="R97" s="6" t="n"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="84" customHeight="1" s="15">
       <c r="A98" s="6" t="n">
@@ -9919,6 +11374,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="84" customHeight="1" s="15">
       <c r="A99" s="6" t="n">
@@ -10009,6 +11479,21 @@
           <t>[TS-06] Class A - all 10 examples in this pattern had empty audio path in grammar.json. The audio MP3s existed on disk but were not wired into examples[].audio. || Fix: Data fix: audio paths populated via tools/fix_remaining_grammar_bugs_2026_05_24.py.</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="84" customHeight="1" s="15">
       <c r="A100" s="6" t="n">
@@ -10095,6 +11580,21 @@
         </is>
       </c>
       <c r="R100" s="6" t="n"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="84" customHeight="1" s="15">
       <c r="A101" s="6" t="n">
@@ -10181,6 +11681,21 @@
         </is>
       </c>
       <c r="R101" s="6" t="n"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="84" customHeight="1" s="15">
       <c r="A102" s="6" t="n">
@@ -10267,6 +11782,21 @@
         </is>
       </c>
       <c r="R102" s="6" t="n"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="84" customHeight="1" s="15">
       <c r="A103" s="6" t="n">
@@ -10357,6 +11887,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="84" customHeight="1" s="15">
       <c r="A104" s="6" t="n">
@@ -10443,6 +11988,21 @@
         </is>
       </c>
       <c r="R104" s="6" t="n"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="84" customHeight="1" s="15">
       <c r="A105" s="6" t="n">
@@ -10529,6 +12089,21 @@
         </is>
       </c>
       <c r="R105" s="6" t="n"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="84" customHeight="1" s="15">
       <c r="A106" s="6" t="n">
@@ -10615,6 +12190,21 @@
         </is>
       </c>
       <c r="R106" s="6" t="n"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="84" customHeight="1" s="15">
       <c r="A107" s="6" t="n">
@@ -10705,6 +12295,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="84" customHeight="1" s="15">
       <c r="A108" s="6" t="n">
@@ -10791,6 +12396,21 @@
         </is>
       </c>
       <c r="R108" s="6" t="n"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="84" customHeight="1" s="15">
       <c r="A109" s="6" t="n">
@@ -10881,6 +12501,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="84" customHeight="1" s="15">
       <c r="A110" s="6" t="n">
@@ -10967,6 +12602,21 @@
         </is>
       </c>
       <c r="R110" s="6" t="n"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="84" customHeight="1" s="15">
       <c r="A111" s="6" t="n">
@@ -11053,6 +12703,21 @@
         </is>
       </c>
       <c r="R111" s="6" t="n"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="84" customHeight="1" s="15">
       <c r="A112" s="6" t="n">
@@ -11139,6 +12804,21 @@
         </is>
       </c>
       <c r="R112" s="6" t="n"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="84" customHeight="1" s="15">
       <c r="A113" s="6" t="n">
@@ -11225,6 +12905,21 @@
         </is>
       </c>
       <c r="R113" s="6" t="n"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="84" customHeight="1" s="15">
       <c r="A114" s="6" t="n">
@@ -11315,6 +13010,21 @@
           <t>[TS-03] Class D - common_mistakes[1] wrong contained '10ぷん まちました。 -&gt; 10ふん' with in-cell arrow. || Fix: Data fix: row repaired via tools/fix_class_d_arrow_cells_2026_05_24.py - extracted the true learner mistake into a clean wrong sentence; diagnostic transformation kept in why field.</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="84" customHeight="1" s="15">
       <c r="A115" s="6" t="n">
@@ -11405,6 +13115,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="84" customHeight="1" s="15">
       <c r="A116" s="6" t="n">
@@ -11491,6 +13216,21 @@
         </is>
       </c>
       <c r="R116" s="6" t="n"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="84" customHeight="1" s="15">
       <c r="A117" s="6" t="n">
@@ -11577,6 +13317,21 @@
         </is>
       </c>
       <c r="R117" s="6" t="n"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="84" customHeight="1" s="15">
       <c r="A118" s="6" t="n">
@@ -11663,6 +13418,21 @@
         </is>
       </c>
       <c r="R118" s="6" t="n"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="84" customHeight="1" s="15">
       <c r="A119" s="6" t="n">
@@ -11749,6 +13519,21 @@
         </is>
       </c>
       <c r="R119" s="6" t="n"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="84" customHeight="1" s="15">
       <c r="A120" s="6" t="n">
@@ -11835,6 +13620,21 @@
         </is>
       </c>
       <c r="R120" s="6" t="n"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="84" customHeight="1" s="15">
       <c r="A121" s="6" t="n">
@@ -11921,6 +13721,21 @@
         </is>
       </c>
       <c r="R121" s="6" t="n"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="84" customHeight="1" s="15">
       <c r="A122" s="6" t="n">
@@ -12007,6 +13822,21 @@
         </is>
       </c>
       <c r="R122" s="6" t="n"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="84" customHeight="1" s="15">
       <c r="A123" s="6" t="n">
@@ -12093,6 +13923,21 @@
         </is>
       </c>
       <c r="R123" s="6" t="n"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="84" customHeight="1" s="15">
       <c r="A124" s="6" t="n">
@@ -12179,6 +14024,21 @@
         </is>
       </c>
       <c r="R124" s="6" t="n"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="84" customHeight="1" s="15">
       <c r="A125" s="6" t="n">
@@ -12265,6 +14125,21 @@
         </is>
       </c>
       <c r="R125" s="6" t="n"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="84" customHeight="1" s="15">
       <c r="A126" s="6" t="n">
@@ -12355,6 +14230,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="84" customHeight="1" s="15">
       <c r="A127" s="6" t="n">
@@ -12445,6 +14335,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="84" customHeight="1" s="15">
       <c r="A128" s="6" t="n">
@@ -12531,6 +14436,21 @@
         </is>
       </c>
       <c r="R128" s="6" t="n"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="84" customHeight="1" s="15">
       <c r="A129" s="6" t="n">
@@ -12621,6 +14541,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="84" customHeight="1" s="15">
       <c r="A130" s="6" t="n">
@@ -12707,6 +14642,21 @@
         </is>
       </c>
       <c r="R130" s="6" t="n"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="84" customHeight="1" s="15">
       <c r="A131" s="6" t="n">
@@ -12793,6 +14743,21 @@
         </is>
       </c>
       <c r="R131" s="6" t="n"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="84" customHeight="1" s="15">
       <c r="A132" s="6" t="n">
@@ -12883,6 +14848,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="84" customHeight="1" s="15">
       <c r="A133" s="6" t="n">
@@ -12973,6 +14953,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="84" customHeight="1" s="15">
       <c r="A134" s="6" t="n">
@@ -13059,6 +15054,21 @@
         </is>
       </c>
       <c r="R134" s="6" t="n"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="84" customHeight="1" s="15">
       <c r="A135" s="6" t="n">
@@ -13149,6 +15159,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="84" customHeight="1" s="15">
       <c r="A136" s="6" t="n">
@@ -13235,6 +15260,21 @@
         </is>
       </c>
       <c r="R136" s="6" t="n"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="84" customHeight="1" s="15">
       <c r="A137" s="6" t="n">
@@ -13321,6 +15361,21 @@
         </is>
       </c>
       <c r="R137" s="6" t="n"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="84" customHeight="1" s="15">
       <c r="A138" s="6" t="n">
@@ -13407,6 +15462,21 @@
         </is>
       </c>
       <c r="R138" s="6" t="n"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="84" customHeight="1" s="15">
       <c r="A139" s="6" t="n">
@@ -13493,6 +15563,21 @@
         </is>
       </c>
       <c r="R139" s="6" t="n"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="84" customHeight="1" s="15">
       <c r="A140" s="6" t="n">
@@ -13579,6 +15664,21 @@
         </is>
       </c>
       <c r="R140" s="6" t="n"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="84" customHeight="1" s="15">
       <c r="A141" s="6" t="n">
@@ -13669,6 +15769,21 @@
           <t>BUG-211 resolved via Option A rewrite v1.16.12</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="84" customHeight="1" s="15">
       <c r="A142" s="6" t="n">
@@ -13755,6 +15870,21 @@
         </is>
       </c>
       <c r="R142" s="6" t="n"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="84" customHeight="1" s="15">
       <c r="A143" s="6" t="n">
@@ -13841,6 +15971,21 @@
         </is>
       </c>
       <c r="R143" s="6" t="n"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="84" customHeight="1" s="15">
       <c r="A144" s="6" t="n">
@@ -13927,6 +16072,21 @@
         </is>
       </c>
       <c r="R144" s="6" t="n"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="84" customHeight="1" s="15">
       <c r="A145" s="6" t="n">
@@ -14013,6 +16173,21 @@
         </is>
       </c>
       <c r="R145" s="6" t="n"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="84" customHeight="1" s="15">
       <c r="A146" s="6" t="n">
@@ -14099,6 +16274,21 @@
         </is>
       </c>
       <c r="R146" s="6" t="n"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="84" customHeight="1" s="15">
       <c r="A147" s="6" t="n">
@@ -14185,6 +16375,21 @@
         </is>
       </c>
       <c r="R147" s="6" t="n"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="84" customHeight="1" s="15">
       <c r="A148" s="6" t="n">
@@ -14275,6 +16480,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="84" customHeight="1" s="15">
       <c r="A149" s="6" t="n">
@@ -14361,6 +16581,21 @@
         </is>
       </c>
       <c r="R149" s="6" t="n"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="84" customHeight="1" s="15">
       <c r="A150" s="6" t="n">
@@ -14447,6 +16682,21 @@
         </is>
       </c>
       <c r="R150" s="6" t="n"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="84" customHeight="1" s="15">
       <c r="A151" s="6" t="n">
@@ -14533,6 +16783,21 @@
         </is>
       </c>
       <c r="R151" s="6" t="n"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="84" customHeight="1" s="15">
       <c r="A152" s="6" t="n">
@@ -14619,6 +16884,21 @@
         </is>
       </c>
       <c r="R152" s="6" t="n"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="84" customHeight="1" s="15">
       <c r="A153" s="6" t="n">
@@ -14705,6 +16985,21 @@
         </is>
       </c>
       <c r="R153" s="6" t="n"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="84" customHeight="1" s="15">
       <c r="A154" s="6" t="n">
@@ -14791,6 +17086,21 @@
         </is>
       </c>
       <c r="R154" s="6" t="n"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="84" customHeight="1" s="15">
       <c r="A155" s="6" t="n">
@@ -14881,6 +17191,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="84" customHeight="1" s="15">
       <c r="A156" s="6" t="n">
@@ -14971,6 +17296,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="84" customHeight="1" s="15">
       <c r="A157" s="6" t="n">
@@ -15057,6 +17397,21 @@
         </is>
       </c>
       <c r="R157" s="6" t="n"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="84" customHeight="1" s="15">
       <c r="A158" s="6" t="n">
@@ -15143,6 +17498,21 @@
         </is>
       </c>
       <c r="R158" s="6" t="n"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="84" customHeight="1" s="15">
       <c r="A159" s="6" t="n">
@@ -15229,6 +17599,21 @@
         </is>
       </c>
       <c r="R159" s="6" t="n"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="84" customHeight="1" s="15">
       <c r="A160" s="6" t="n">
@@ -15315,6 +17700,21 @@
         </is>
       </c>
       <c r="R160" s="6" t="n"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="84" customHeight="1" s="15">
       <c r="A161" s="6" t="n">
@@ -15401,6 +17801,21 @@
         </is>
       </c>
       <c r="R161" s="6" t="n"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="84" customHeight="1" s="15">
       <c r="A162" s="6" t="n">
@@ -15487,6 +17902,21 @@
         </is>
       </c>
       <c r="R162" s="6" t="n"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="84" customHeight="1" s="15">
       <c r="A163" s="6" t="n">
@@ -15577,6 +18007,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="84" customHeight="1" s="15">
       <c r="A164" s="6" t="n">
@@ -15663,6 +18108,21 @@
         </is>
       </c>
       <c r="R164" s="6" t="n"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="84" customHeight="1" s="15">
       <c r="A165" s="6" t="n">
@@ -15749,6 +18209,21 @@
         </is>
       </c>
       <c r="R165" s="6" t="n"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="84" customHeight="1" s="15">
       <c r="A166" s="6" t="n">
@@ -15835,6 +18310,21 @@
         </is>
       </c>
       <c r="R166" s="6" t="n"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="84" customHeight="1" s="15">
       <c r="A167" s="6" t="n">
@@ -15921,6 +18411,21 @@
         </is>
       </c>
       <c r="R167" s="6" t="n"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="84" customHeight="1" s="15">
       <c r="A168" s="6" t="n">
@@ -16007,6 +18512,21 @@
         </is>
       </c>
       <c r="R168" s="6" t="n"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="84" customHeight="1" s="15">
       <c r="A169" s="6" t="n">
@@ -16093,6 +18613,21 @@
         </is>
       </c>
       <c r="R169" s="6" t="n"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="84" customHeight="1" s="15">
       <c r="A170" s="6" t="n">
@@ -16183,6 +18718,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="84" customHeight="1" s="15">
       <c r="A171" s="6" t="n">
@@ -16273,6 +18823,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="84" customHeight="1" s="15">
       <c r="A172" s="6" t="n">
@@ -16359,6 +18924,21 @@
         </is>
       </c>
       <c r="R172" s="6" t="n"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="84" customHeight="1" s="15">
       <c r="A173" s="6" t="n">
@@ -16449,6 +19029,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="84" customHeight="1" s="15">
       <c r="A174" s="6" t="n">
@@ -16535,6 +19130,21 @@
         </is>
       </c>
       <c r="R174" s="6" t="n"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="84" customHeight="1" s="15">
       <c r="A175" s="6" t="n">
@@ -16621,6 +19231,21 @@
         </is>
       </c>
       <c r="R175" s="6" t="n"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="84" customHeight="1" s="15">
       <c r="A176" s="6" t="n">
@@ -16711,6 +19336,21 @@
           <t>[TS-03] FP-16 - auto-check flagged 'empty wrong/right' on a register_variant entry. These entries use a different schema (kind=register_variant, form_a/form_b/label_a/label_b) where both forms are valid; they are not error wrong/right pairs. || Fix: Test-logic fix: tools/grammar_auto_checks.py + grammar_horizontal_checks.py + export_grammar_for_review.py + fix_class_e_paren_context_2026_05_24.py now all skip rows where kind='register_variant'. No</t>
         </is>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="84" customHeight="1" s="15">
       <c r="A177" s="6" t="n">
@@ -16797,6 +19437,21 @@
         </is>
       </c>
       <c r="R177" s="6" t="n"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="84" customHeight="1" s="15">
       <c r="A178" s="6" t="n">
@@ -16883,6 +19538,21 @@
         </is>
       </c>
       <c r="R178" s="6" t="n"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="84" customHeight="1" s="15">
       <c r="A179" s="6" t="n">
@@ -16969,6 +19639,21 @@
         </is>
       </c>
       <c r="R179" s="6" t="n"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Claude (LLM, programmatic schema)</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Pending — awaiting native-teacher pass</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/N5/test/categorized testing/CategorizedtestScenarios.xlsx
+++ b/N5/test/categorized testing/CategorizedtestScenarios.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L95" s="10" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L96" s="10" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L97" s="10" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="K98" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L98" s="10" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L99" s="12" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>Partial: only 1/10 examples visibly contain the pattern form (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: only 1/10 examples visibly contain the pattern form (heuristic; conjugated forms (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L102" s="10" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L103" s="10" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L104" s="10" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L105" s="10" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="K108" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L108" s="10" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>Partial: only 1/10 examples visibly contain the pattern form (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: only 1/10 examples visibly contain the pattern form (heuristic; conjugated forms (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="K139" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L139" s="10" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="K140" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L140" s="10" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="K142" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L142" s="10" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="K143" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L143" s="10" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="K146" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L146" s="10" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K147" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L147" s="10" t="inlineStr">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="K148" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L148" s="10" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="K165" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L165" s="10" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="K166" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L166" s="10" t="inlineStr">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="K167" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L167" s="10" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="K169" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L169" s="10" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="K170" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L170" s="10" t="inlineStr">
@@ -18785,7 +18785,7 @@
       </c>
       <c r="K171" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L171" s="10" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="K172" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L172" s="10" t="inlineStr">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="K174" s="10" t="inlineStr">
         <is>
-          <t>Partial: no example contains the pattern form (heuristic; conjugated forms may not match  (programmatic-v2, 2026-05-24)</t>
+          <t>Partial: NA-heuristic-limit: pattern form not found by static substring match (conjugatio (programmatic-v2, 2026-05-24)</t>
         </is>
       </c>
       <c r="L174" s="10" t="inlineStr">

--- a/N5/test/categorized testing/CategorizedtestScenarios.xlsx
+++ b/N5/test/categorized testing/CategorizedtestScenarios.xlsx
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M53" s="10" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M55" s="10" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="L56" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M56" s="10" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M57" s="10" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="L58" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M59" s="10" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="L62" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="L64" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M64" s="10" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M65" s="10" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M66" s="10" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="L68" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M68" s="10" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="L94" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="L96" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="L102" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
@@ -11939,7 +11939,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="L112" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I114" s="12" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I126" s="12" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I132" s="12" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="L138" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="L140" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="L141" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M141" s="10" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="L142" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="L143" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M143" s="10" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="L144" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M144" s="10" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="L145" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M145" s="10" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="L146" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="L147" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M147" s="10" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I148" s="12" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="L148" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M148" s="10" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="L149" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M149" s="10" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="L150" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M150" s="10" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="L151" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M151" s="10" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="L152" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M152" s="10" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="L153" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M153" s="10" t="inlineStr">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="L154" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M154" s="10" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="L155" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M155" s="10" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I156" s="12" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="L156" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M156" s="10" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -17368,7 +17368,7 @@
       </c>
       <c r="L157" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M157" s="10" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="L158" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M158" s="10" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -17570,7 +17570,7 @@
       </c>
       <c r="L159" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M159" s="10" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="L160" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M160" s="10" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="L161" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M161" s="10" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="L162" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="L163" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M163" s="10" t="inlineStr">
@@ -18059,7 +18059,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="L164" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="L165" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M165" s="10" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="L166" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M166" s="10" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="L167" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M167" s="10" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="L168" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M168" s="10" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="L169" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M169" s="10" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I170" s="12" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="L170" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M170" s="10" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I171" s="12" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="L171" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M171" s="10" t="inlineStr">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="L172" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M172" s="10" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I173" s="12" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="L173" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M173" s="10" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="L174" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M174" s="10" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="L175" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M175" s="10" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I176" s="12" t="inlineStr">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="L176" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M176" s="10" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="L177" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M177" s="10" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L178" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M178" s="10" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (43 kana↔kanji intentional pedagogical variants + 5 intentional contrast pairs annotated + 6 accidental near-dups dropped). Reviewer v5 corrected (2026-05-24).</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="L179" s="10" t="inlineStr">
         <is>
-          <t>Pass (programmatic-v2, 2026-05-24)</t>
+          <t>Pass (structural audit: 1768/1768 audio refs resolve in audio_manifest.json + exist on disk; commit 1046ffcb).</t>
         </is>
       </c>
       <c r="M179" s="10" t="inlineStr">

--- a/N5/test/categorized testing/CategorizedtestScenarios.xlsx
+++ b/N5/test/categorized testing/CategorizedtestScenarios.xlsx
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" style="15" min="1" max="1"/>
@@ -1355,6 +1355,39 @@
           <t xml:space="preserve">Re-run 2026-05-24: Pass=178 Fail=0 Partial=0 N/A=0 (of 178 patterns). </t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TS-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wrong/right pair — struck-off line must be a real linguistic error</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>For every common_mistakes and wrong_corrected_pair entry, the WRONG (struck-off) line must contain an actual linguistic error a learner could make — not a stylistic, register, or kanji-vs-kana preference where both forms are valid Japanese.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pattern/explanation/example consistency (6.2) + Japanese language correctness (6.1)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1. Open the pattern's interactive page. 2. For each common_mistakes / wrong_corrected_pair entry: read the WRONG (struck-off) line. 3. Ask: is this actually wrong Japanese a native speaker would not write, OR is it just a stylistic difference (e.g., kanji vs kana of the same word) where both forms are valid? 4. If only stylistically different — flag as defect. 5. The "why" field should diagnose a real error, not a style preference.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Every WRONG line is a genuine learner mistake. No kanji-vs-kana over-reach (e.g., 二つ vs ふたつ where both are valid). No "use form X in formal context" framed as wrong/right.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20146,7 +20179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="15" min="1" max="1"/>
@@ -20198,19 +20231,49 @@
     <row r="2" ht="60" customHeight="1" s="15">
       <c r="A2" s="8" t="inlineStr">
         <is>
+          <t>TS-01</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>MCQ answer-count integrity — exactly one correct (or exactly one wrong) per question</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>For every paper question, the choices array must contain exactly the right number of correct/wrong answers given the question type. "Pick the correct answer" questions: exactly 1 correct, 3 wrong. "Pick the wrong answer" questions (rare, explicitly marked): exactly 1 wrong, 3 correct. No question may have 0 correct/wrong or multiple ambiguously-correct answers.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Paper/question integrity (6.4)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1. Open the paper category sheet (moji / goi / bunpou / dokkai). 2. For each question in data/papers/&lt;cat&gt;/paper-N.json: identify the question type from the stem ("pick the correct" is default; "pick the wrong" is marked explicitly). 3. Count correct answers among the 4 choices by checking the rationale + correctIndex. 4. Assert: pick-correct has exactly 1 correct (matching correctIndex) + 3 genuinely-wrong distractors; pick-wrong has exactly 1 wrong (matching correctIndex) + 3 genuinely-correct alternatives. 5. Flag if 2+ choices could be marked correct, or if the "wrong" distractor is also technically valid.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Exactly one correct answer for pick-correct questions; exactly one wrong answer for pick-wrong questions. No ambiguous distractors. correctIndex matches the unique correct/wrong choice.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>[Phase 2 — scenarios for Test Papers to be defined]</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Test Papers = past papers / mock papers. Future scenarios should check: paper structure matches official JLPT, answer keys correct, time-limit realistic, score-bands accurate.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>